--- a/experiments/results/resnet34/CIFAR-10/DICE/adaptive/max/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/DICE/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -813,6 +813,349 @@
       <c r="O9" s="5" t="inlineStr">
         <is>
           <t>dice_p=85,ash_p=None,react_th=None,scale_th=3.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>98.38</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>92.84999999999999</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>96.83</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>97.59</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=70,ash_p=None,react_th=None,scale_th=3.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>93.16</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>97.68000000000001</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=70,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>92.95999999999999</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>98.39</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>93.23</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=80,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>92.81999999999999</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=50,ash_p=None,react_th=None,scale_th=3.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>92.95999999999999</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>92.95999999999999</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
